--- a/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/temp_out2.xlsx
+++ b/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/temp_out2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +495,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>150 TEXTURISED POLYESTER</t>
+          <t>150/48 TEXTURISED POLYESTER</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>121</v>
+        <v>121.1</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>1201</v>
       </c>
       <c r="C20" t="n">
         <v>15</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1013.93</v>
+        <v>0.93</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>257.3</v>
+        <v>6000.3</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -723,9 +723,7 @@
           <t>250 HT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>3</v>
       </c>
@@ -950,18 +948,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>75/2 TXP-TPM 800/700</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="n">
-        <v>10</v>
-      </c>
+          <t>75/2 TEXTURISED POLYESTER</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>330.11</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>75/3 TXP-TPM 800/560</t>
+          <t>75/2 TXP-TPM 800/700</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -972,37 +970,48 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>840 HI-TENACITY NYLON 6 YARN</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>704.12</v>
-      </c>
+          <t>75/3 TXP-TPM 800/560</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>840 HI-TENACITY NYLON 66 YARN</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>840 HI-TENACITY NYLON 6 YARN</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>704.12</v>
+      </c>
       <c r="C49" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>840 HI-TENACITY NYLON 66 YARN</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>840 HT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B51" t="n">
         <v>329.88</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C51" t="n">
         <v>15</v>
       </c>
     </row>
